--- a/NPS - matriz-tijuca.xlsx
+++ b/NPS - matriz-tijuca.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="454">
   <si>
     <t>userId</t>
   </si>
@@ -31,6 +31,9 @@
     <t>userEmail</t>
   </si>
   <si>
+    <t>tipoRespondente</t>
+  </si>
+  <si>
     <t>answeredAt</t>
   </si>
   <si>
@@ -88,21 +91,365 @@
     <t>AÇÃO</t>
   </si>
   <si>
-    <t>Última atualização: 22/03/2026 16:30</t>
+    <t>Última atualização: 25/03/2026 18:30</t>
+  </si>
+  <si>
+    <t>698bc812d7b0f7a720ef4319</t>
+  </si>
+  <si>
+    <t>69b86abc21c08e4e2eff1f02</t>
+  </si>
+  <si>
+    <t>Queremos ouvir a sua opinião</t>
+  </si>
+  <si>
+    <t>matriz-tijuca</t>
+  </si>
+  <si>
+    <t>ISADORA TEIXEIRA COELHO16</t>
+  </si>
+  <si>
+    <t>ruteleiateixeira@gmail.com</t>
+  </si>
+  <si>
+    <t>responsavel</t>
+  </si>
+  <si>
+    <t>2026-03-25T21:02:22.713Z</t>
+  </si>
+  <si>
+    <t>Acho que alguns profissionais deixam a desejar</t>
+  </si>
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>698bc812d7b0f7f91def433b</t>
+  </si>
+  <si>
+    <t>GABRIELA DE PAULA LINS</t>
+  </si>
+  <si>
+    <t>gabilins89@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:46:33.344Z</t>
+  </si>
+  <si>
+    <t>10 - Extremamente provável</t>
+  </si>
+  <si>
+    <t>Tenho gostado muito das impressões desses primeiros meses. Observando e aguardando as próximas fases do ano, mas bastante feliz com a escolha.</t>
+  </si>
+  <si>
+    <t>6 - Muito Satisfeito</t>
+  </si>
+  <si>
+    <t>As vezes me perco um pouco no layers. Fiz um pagamento da atividade extra JJ mas na verdade queria ter inscrito ele no teatro. Tentei mandar msg por lá no mesmo dia pedindo estorno, mas não sei pra onde foi. Perdi o prazo do teatro, mas aí foi minha falta de entendimento mesmo com a plataforma e fui ajudada pela secretaria... Enfim, ajustando os ponteiros mas creio que seja um sistema muito bom e estou curtindo tudo da escola! Inclusive e principalmente o incentivo aos alunos.</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>693221cc137069679a062cf5</t>
+  </si>
+  <si>
+    <t>69b89948ff994cd629640f99</t>
+  </si>
+  <si>
+    <t>STELLA DA COSTA FERNANDES</t>
+  </si>
+  <si>
+    <t>stellamt25183807@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>estudante</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:43:15.431Z</t>
+  </si>
+  <si>
+    <t>Ótima experiência.</t>
+  </si>
+  <si>
+    <t>Aluno</t>
+  </si>
+  <si>
+    <t>6960467df1a4c120b9b7696b</t>
+  </si>
+  <si>
+    <t>MARINA MORENA CAZES CORRÊA</t>
+  </si>
+  <si>
+    <t>marinamt25195389@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:38:54.241Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os professores são bons e pacientes, além de o sistema de estudo ser bem </t>
+  </si>
+  <si>
+    <t>69658c84481ebfda519c330e</t>
+  </si>
+  <si>
+    <t>CLARISSA DA CUNHA MENEZES</t>
+  </si>
+  <si>
+    <t>clarissamt25194325@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:37:41.815Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a escola é muito boa, com o ensino bom e qualquer pessoa consegue se encaixar 
+</t>
+  </si>
+  <si>
+    <t>6983dedebb033170524cdb92</t>
+  </si>
+  <si>
+    <t>ROMULO TEIXEIRA CARVALHO</t>
+  </si>
+  <si>
+    <t>romuloteixeirac@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:22:33.835Z</t>
+  </si>
+  <si>
+    <t>Nesses 3 meses que os meus filhos estão matriculados, sempre fui muito bem atendido por toda equipe Matriz.</t>
+  </si>
+  <si>
+    <t>Poderiam ter colocado as aulas da 3a. Série que as quintas feiras terminam 15:00 e as sextas às 16:20, para aulas aos sábados pela manhã.</t>
+  </si>
+  <si>
+    <t>679cc0bad8b0239d98ae7d04</t>
+  </si>
+  <si>
+    <t>ALEXANDER MONTEIRO CERQUEIRA</t>
+  </si>
+  <si>
+    <t>alexander.cerqueira@yahoo.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:59:45.149Z</t>
+  </si>
+  <si>
+    <t>Pela atenção e acompanhamento com os alunos.</t>
+  </si>
+  <si>
+    <t>6984d25e99492b7866856a35</t>
+  </si>
+  <si>
+    <t>DANIELE REGO FERREIRA</t>
+  </si>
+  <si>
+    <t>danielekauaiferreira@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:56:52.643Z</t>
+  </si>
+  <si>
+    <t>Ótimo colégio!!</t>
+  </si>
+  <si>
+    <t>698bc812d7b0f7c8eaef4335</t>
+  </si>
+  <si>
+    <t>MARIA HELENA INACIO DE SANTANA</t>
+  </si>
+  <si>
+    <t>santanahelena712@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:48:42.143Z</t>
+  </si>
+  <si>
+    <t>Sim recomendo!</t>
+  </si>
+  <si>
+    <t>Olá estou satisfeito com td organização e acolhimento do Matriz Educação e ensino.</t>
+  </si>
+  <si>
+    <t>68e1b62183f61bb983135c1c</t>
+  </si>
+  <si>
+    <t>THIAGO DE SOUZA FAGUNDES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>fagundesthiago2016@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-24T23:25:54.532Z</t>
+  </si>
+  <si>
+    <t>Vejo acolhimento,  desempenho dos professores e excelente ensino.</t>
+  </si>
+  <si>
+    <t>67b49e6e5655557b7b04a6f9</t>
+  </si>
+  <si>
+    <t>ARTHUR SANTOS CERQUEIRA</t>
+  </si>
+  <si>
+    <t>arthurmt25157835@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-24T23:06:00.343Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pela qualidade do ensino </t>
+  </si>
+  <si>
+    <t>698e6b2e5c7622064a3291d0</t>
+  </si>
+  <si>
+    <t>VINCENZO MAGALHÃES SALERNO</t>
+  </si>
+  <si>
+    <t>vincenzomt26202499@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:47:32.016Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eu não tenho muito contato com outros estudantes perto da minha residência ou de onde estiver mas não é impossível </t>
+  </si>
+  <si>
+    <t>Sugestão de melhoria na aplicação das provas
+Uma possível solução seria aumentar o tempo de realização das provas ou reorganizar a distribuição das disciplinas ao longo da semana. Por exemplo, poderia haver dias específicos para determinadas matérias, como História e Geografia na segunda-feira, ou até mesmo concentrar três disciplinas em um único dia e, nos demais, dividir as outras de forma equilibrada.
+Caso não seja possível ampliar significativamente o tempo para todas as matérias, uma alternativa seria conceder um tempo adicional, pelo menos, para disciplinas que exigem maior desenvolvimento, como Matemática e Redação.</t>
+  </si>
+  <si>
+    <t>Detrator</t>
+  </si>
+  <si>
+    <t>6984d0870d95f30333eba9a7</t>
+  </si>
+  <si>
+    <t>IVANILDA DE SOUSA RODRIGUES</t>
+  </si>
+  <si>
+    <t>rodriguenilce1@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-24T01:59:28.275Z</t>
+  </si>
+  <si>
+    <t>Pelo fato que deveria ter mais um tempo de avaliação de redação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acho que deveria ter mais um tempo de avaliação de redação </t>
+  </si>
+  <si>
+    <t>6941f3dfa0ddde04e45ad7b2</t>
+  </si>
+  <si>
+    <t>DANIELLA CRISTINA DOS SANTOS DA ROCHA</t>
+  </si>
+  <si>
+    <t>danicrisrock@hotmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-24T00:21:20.836Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Até o momento temos tido uma boa comunicação com a escola.
+</t>
+  </si>
+  <si>
+    <t>No geral estamos satisfeitos, mas me preocupa a falta de monitoramento em sala de aula. Recebi relato de casos de sumiço de material escolar dos alunos (meu filho foi um dos que foram prejudicados). 
+Na última sexta (20/03/26) um colega apalpou (como que revistando) e em seguida abaixou as calças do outro desconfiando que esse havia pego algo de seu material e foi afastado bruscamente pelo que se sentiu constrangido. 
+Nada disso foi levado ao conhecimento dos professores , da Coordenação/ Direção e nem identificado por não haver monitoramento de câmeras. 
+Considero um ponto importante a ser analisado. Além de palestras/ conversas sobre  respeito e valores, reforçando a educação transmitinda em casa.</t>
+  </si>
+  <si>
+    <t>693221cc137069f447062c3b</t>
+  </si>
+  <si>
+    <t>LUIS MIGUEL ARAUJO FORRESTER</t>
+  </si>
+  <si>
+    <t>luismt25183369@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-23T23:11:41.868Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ótimos professores, direção dedicada ao extremo em cada detalhe do aluno e pais.
+</t>
+  </si>
+  <si>
+    <t>693221cc137069c563062c41</t>
+  </si>
+  <si>
+    <t>MARIANA TRIGO JORDÃO MOURA</t>
+  </si>
+  <si>
+    <t>marianamt25186685@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-23T22:23:43.795Z</t>
+  </si>
+  <si>
+    <t>Gosto do ambiente escolar e dos funcionários mas ainda estou me adaptando.</t>
+  </si>
+  <si>
+    <t>Seria muito bom ter relógios nas salas de aula, para melhor administração do tempo durante as avaliações.</t>
+  </si>
+  <si>
+    <t>697b833f567cd3e099db63bc</t>
+  </si>
+  <si>
+    <t>EUDOXIA MARIA FORTUNA</t>
+  </si>
+  <si>
+    <t>fortunalaryssa9@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T21:01:29.162Z</t>
+  </si>
+  <si>
+    <t>A instituição conta com uma ótima infraestrutura e um ambiente bem estruturado. Destaco também a qualidade da equipe de coordenação, sempre prestativa, organizada e atenciosa. Estou muito satisfeita com a experiência até o momento.</t>
+  </si>
+  <si>
+    <t>693a0b1a8bf015548e97b979</t>
+  </si>
+  <si>
+    <t>PEDRO PAULO ARIGONI DE SOUZA</t>
+  </si>
+  <si>
+    <t>pedromt25191263@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-23T14:22:05.116Z</t>
+  </si>
+  <si>
+    <t>É uma escola muito boa, com ótimo professores e funcionários que fazem de tudo pra extrair o nosso melhor.</t>
+  </si>
+  <si>
+    <t>67903682b39270be0089b2c1</t>
+  </si>
+  <si>
+    <t>KARINA MARIA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>karinamnogueira@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T10:15:17.783Z</t>
+  </si>
+  <si>
+    <t>Bom desenvolvimento do meu filho.</t>
   </si>
   <si>
     <t>693221cc137069dc96062d00</t>
   </si>
   <si>
-    <t>69b89948ff994cd629640f99</t>
-  </si>
-  <si>
-    <t>Queremos ouvir a sua opinião</t>
-  </si>
-  <si>
-    <t>matriz-tijuca</t>
-  </si>
-  <si>
     <t>PEDRO LUCAS SIQUEIRA BENICÁ</t>
   </si>
   <si>
@@ -112,28 +459,13 @@
     <t>2026-03-22T00:48:32.4Z</t>
   </si>
   <si>
-    <t>10 - Extremamente provável</t>
-  </si>
-  <si>
     <t xml:space="preserve">Muito </t>
   </si>
   <si>
-    <t>6 - Muito Satisfeito</t>
-  </si>
-  <si>
     <t xml:space="preserve">Excelente </t>
   </si>
   <si>
-    <t>Aluno</t>
-  </si>
-  <si>
-    <t>Promotor</t>
-  </si>
-  <si>
     <t>69658c84481ebf6a309c3306</t>
-  </si>
-  <si>
-    <t>69b86abc21c08e4e2eff1f02</t>
   </si>
   <si>
     <t>LOURENA</t>
@@ -150,12 +482,6 @@
   <si>
     <t>Eu estou gostando muito da escola. Tenho alguns pontos a estacar que acredito que deveria melhorar. Utilizar o livro de forma completa inclusive no que tange aos exercícios, observo muitos exercícios em
 Branco pois o professor não direciona fazer. Ademais acredito que algumas exceções de ocorrer reuniões on line com a coordenação e os pais pois nem todos os pais conseguem sair do trabalho com facilidade. Temos ciência da importância de uma reunião presencia mas existem exceções que devem ser analisadas.</t>
-  </si>
-  <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Neutro</t>
   </si>
   <si>
     <t>69658c84481ebf95ab9c331f</t>
@@ -930,9 +1256,6 @@
   </si>
   <si>
     <t>Ainda não conheço a escola</t>
-  </si>
-  <si>
-    <t>Detrator</t>
   </si>
   <si>
     <t>69658c84481ebf47259c3307</t>
@@ -1368,28 +1691,29 @@
     <col customWidth="1" min="2" max="2" width="21.75"/>
     <col customWidth="1" min="3" max="3" width="22.38"/>
     <col customWidth="1" min="4" max="4" width="9.88"/>
-    <col customWidth="1" min="5" max="5" width="35.63"/>
+    <col customWidth="1" min="5" max="5" width="36.5"/>
     <col customWidth="1" min="6" max="6" width="35.38"/>
-    <col customWidth="1" min="7" max="7" width="20.5"/>
-    <col customWidth="1" min="8" max="8" width="68.0"/>
-    <col customWidth="1" min="9" max="9" width="255.63"/>
-    <col customWidth="1" min="10" max="10" width="67.63"/>
-    <col customWidth="1" min="11" max="11" width="71.63"/>
-    <col customWidth="1" min="12" max="12" width="74.13"/>
-    <col customWidth="1" min="13" max="13" width="49.25"/>
-    <col customWidth="1" min="14" max="14" width="69.88"/>
-    <col customWidth="1" min="15" max="15" width="35.63"/>
-    <col customWidth="1" min="16" max="16" width="50.25"/>
-    <col customWidth="1" min="17" max="17" width="69.38"/>
-    <col customWidth="1" min="18" max="18" width="62.0"/>
-    <col customWidth="1" min="19" max="19" width="395.75"/>
-    <col customWidth="1" min="20" max="20" width="14.25"/>
-    <col customWidth="1" min="21" max="21" width="7.75"/>
-    <col customWidth="1" min="22" max="22" width="12.75"/>
-    <col customWidth="1" min="23" max="23" width="24.13"/>
-    <col customWidth="1" min="24" max="24" width="16.38"/>
-    <col customWidth="1" min="25" max="25" width="5.25"/>
-    <col customWidth="1" min="26" max="26" width="28.63"/>
+    <col customWidth="1" min="7" max="7" width="13.38"/>
+    <col customWidth="1" min="8" max="8" width="20.5"/>
+    <col customWidth="1" min="9" max="9" width="68.0"/>
+    <col customWidth="1" min="10" max="10" width="255.63"/>
+    <col customWidth="1" min="11" max="11" width="67.63"/>
+    <col customWidth="1" min="12" max="12" width="71.63"/>
+    <col customWidth="1" min="13" max="13" width="74.13"/>
+    <col customWidth="1" min="14" max="14" width="49.25"/>
+    <col customWidth="1" min="15" max="15" width="69.88"/>
+    <col customWidth="1" min="16" max="16" width="35.63"/>
+    <col customWidth="1" min="17" max="17" width="50.25"/>
+    <col customWidth="1" min="18" max="18" width="69.38"/>
+    <col customWidth="1" min="19" max="19" width="62.0"/>
+    <col customWidth="1" min="20" max="20" width="395.75"/>
+    <col customWidth="1" min="21" max="21" width="14.25"/>
+    <col customWidth="1" min="22" max="22" width="7.75"/>
+    <col customWidth="1" min="23" max="23" width="12.75"/>
+    <col customWidth="1" min="24" max="24" width="24.13"/>
+    <col customWidth="1" min="25" max="25" width="16.38"/>
+    <col customWidth="1" min="26" max="26" width="5.25"/>
+    <col customWidth="1" min="27" max="27" width="28.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1471,159 +1795,166 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
         <v>34</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>35</v>
+      <c r="K2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>4.0</v>
       </c>
       <c r="P2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" s="2" t="s">
+        <v>4.0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="3"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="2">
         <v>4.0</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R3" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -1634,2502 +1965,2610 @@
       <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="2">
-        <v>9.0</v>
+      <c r="H4" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="O4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V4" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" s="3"/>
+      <c r="V5" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="L6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>5.0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" s="2"/>
       <c r="U6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V6" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S7" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="M8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>5.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="R8" s="2">
+        <v>5.0</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R9" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="T9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S10" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V11" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="2">
-        <v>9.0</v>
+        <v>51</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>35</v>
+        <v>96</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5.0</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O12" s="2">
         <v>5.0</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R12" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="s">
+      <c r="P12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>4.0</v>
+        <v>51</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M13" s="2">
         <v>5.0</v>
       </c>
-      <c r="N13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O13" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T13" s="2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="2">
+        <v>33</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="2">
         <v>8.0</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>35</v>
+      <c r="J15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>4.0</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="O15" s="2">
+        <v>4.0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R15" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>110</v>
+        <v>44</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S15" s="2">
+        <v>4.0</v>
       </c>
       <c r="T15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="2">
-        <v>8.0</v>
+        <v>51</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J16" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="K16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L16" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N16" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O16" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>4.0</v>
+        <v>42</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>35</v>
+        <v>125</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5.0</v>
       </c>
       <c r="L17" s="2">
         <v>5.0</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>35</v>
+      <c r="M17" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5.0</v>
       </c>
       <c r="O17" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>121</v>
+        <v>44</v>
+      </c>
+      <c r="S17" s="2">
+        <v>4.0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V17" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N18" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V18" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>5.0</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="R19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T19" s="2"/>
       <c r="U19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L20" s="2">
-        <v>5.0</v>
+        <v>141</v>
+      </c>
+      <c r="K20" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M20" s="2">
         <v>5.0</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P20" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V20" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H21" s="2">
-        <v>9.0</v>
+        <v>51</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P21" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="Q21" s="2">
         <v>5.0</v>
       </c>
-      <c r="R21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S21" s="2"/>
+      <c r="R21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8.0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>35</v>
+        <v>152</v>
+      </c>
+      <c r="K22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>4.0</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>148</v>
+        <v>44</v>
+      </c>
+      <c r="R22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>5.0</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V22" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
+      </c>
+      <c r="I23" s="2">
+        <v>9.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L23" s="2">
-        <v>5.0</v>
+        <v>158</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O23" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T23" s="2"/>
       <c r="U23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="T24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P25" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T25" s="2"/>
       <c r="U25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V25" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>168</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="2">
-        <v>4.0</v>
+        <v>42</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M26" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T26" s="2"/>
       <c r="U26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V26" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>33</v>
+        <v>177</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>174</v>
+        <v>42</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S27" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>178</v>
+        <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>33</v>
+        <v>183</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>179</v>
+        <v>42</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S28" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="N28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T28" s="2" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V28" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>33</v>
+        <v>189</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J29" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P29" s="2">
-        <v>4.0</v>
+        <v>44</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="T29" s="2"/>
       <c r="U29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>189</v>
+        <v>51</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="T30" s="2"/>
       <c r="U30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V30" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>195</v>
+        <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
+      </c>
+      <c r="I31" s="2">
+        <v>9.0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L31" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N31" s="2">
         <v>5.0</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="T31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R31" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="I32" s="2">
+        <v>8.0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>33</v>
+        <v>209</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>207</v>
+        <v>42</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>35</v>
+        <v>210</v>
+      </c>
+      <c r="K33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5.0</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>211</v>
+        <v>51</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8.0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>35</v>
+        <v>215</v>
+      </c>
+      <c r="K34" s="2">
+        <v>5.0</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>213</v>
+        <v>44</v>
+      </c>
+      <c r="S34" s="2">
+        <v>5.0</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>46</v>
+        <v>216</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V34" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H35" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>218</v>
+        <v>33</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I35" s="2">
+        <v>8.0</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="K35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>35</v>
+        <v>4.0</v>
+      </c>
+      <c r="L35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P35" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q35" s="2">
         <v>5.0</v>
       </c>
       <c r="R35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T35" s="2"/>
       <c r="U35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V35" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="H36" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J36" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L36" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M36" s="2">
+        <v>5.0</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P36" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q36" s="2">
-        <v>5.0</v>
+      <c r="Q36" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="R36" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="T36" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V36" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>228</v>
+        <v>51</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>33</v>
+        <v>231</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J37" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L37" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="O37" s="2">
+        <v>5.0</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R37" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>230</v>
+        <v>44</v>
       </c>
       <c r="T37" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V37" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H38" s="2">
-        <v>8.0</v>
+        <v>51</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>35</v>
+        <v>238</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P38" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q38" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V38" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H39" s="2">
-        <v>9.0</v>
+        <v>51</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="J39" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L39" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O39" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R39" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S39" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T39" s="2" t="s">
-        <v>37</v>
+        <v>243</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H40" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J40" s="2">
-        <v>3.0</v>
+        <v>33</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I40" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="K40" s="2">
         <v>5.0</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>35</v>
+      <c r="L40" s="2">
+        <v>5.0</v>
       </c>
       <c r="M40" s="2">
         <v>5.0</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>35</v>
+      <c r="N40" s="2">
+        <v>5.0</v>
       </c>
       <c r="O40" s="2">
         <v>5.0</v>
@@ -4138,798 +4577,830 @@
         <v>5.0</v>
       </c>
       <c r="Q40" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R40" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="T40" s="2" t="s">
+        <v>5.0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>250</v>
+        <v>33</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>33</v>
+        <v>252</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J41" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K41" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M41" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O41" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="P41" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R41" s="2">
-        <v>4.0</v>
+        <v>44</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V41" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>256</v>
+        <v>51</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>33</v>
+        <v>258</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>257</v>
+        <v>42</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="L42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>5.0</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="O42" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P42" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V42" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H43" s="2">
-        <v>7.0</v>
+        <v>51</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J43" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K43" s="2">
-        <v>4.0</v>
+        <v>42</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O43" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P43" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R43" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S43" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T43" s="2" t="s">
-        <v>37</v>
+        <v>265</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V43" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H44" s="2">
-        <v>7.0</v>
+        <v>51</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>267</v>
+        <v>42</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L44" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O44" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="P44" s="2">
-        <v>2.0</v>
+        <v>270</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="Q44" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R44" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S44" s="2"/>
-      <c r="T44" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T44" s="2"/>
       <c r="U44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V44" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>271</v>
+        <v>51</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>272</v>
+        <v>42</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>35</v>
+        <v>275</v>
+      </c>
+      <c r="K45" s="2">
+        <v>4.0</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="N45" s="2">
+        <v>5.0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="P45" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="T45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V45" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V45" s="3"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>277</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>33</v>
+        <v>279</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J46" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K46" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T46" s="2"/>
       <c r="U46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V46" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>282</v>
+        <v>51</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>33</v>
+        <v>284</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J47" s="2">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M47" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N47" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P47" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q47" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R47" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="T47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V47" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H48" s="2">
-        <v>7.0</v>
+        <v>51</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="K48" s="2">
+        <v>5.0</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>4.0</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>290</v>
+        <v>44</v>
       </c>
       <c r="T48" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>294</v>
+        <v>51</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>33</v>
+        <v>295</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J49" s="2">
-        <v>4.0</v>
+        <v>42</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O49" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>296</v>
+        <v>44</v>
       </c>
       <c r="T49" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V49" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V49" s="3"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="H50" s="2">
-        <v>6.0</v>
+        <v>33</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>301</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="J50" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="K50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L50" s="2">
-        <v>3.0</v>
+        <v>42</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M50" s="2">
         <v>5.0</v>
       </c>
-      <c r="N50" s="2">
-        <v>5.0</v>
+      <c r="N50" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q50" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="R50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S50" s="2"/>
+        <v>5.0</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="T50" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V50" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U50" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>306</v>
+        <v>51</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>33</v>
+        <v>307</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>307</v>
+        <v>42</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>35</v>
+        <v>308</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L51" s="2">
-        <v>5.0</v>
+        <v>44</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="T51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U51" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V51" s="3"/>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>310</v>
@@ -4938,471 +5409,1861 @@
         <v>311</v>
       </c>
       <c r="G52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="I52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="J52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M52" s="2">
-        <v>4.0</v>
+      <c r="K52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="T52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V52" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U52" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="G53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="I53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I53" s="2" t="s">
+      <c r="K53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T53" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="T53" s="2" t="s">
+      <c r="U53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V53" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V53" s="3"/>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="G54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="I54" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J54" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="K54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="L54" s="2">
+        <v>5.0</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S54" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="T54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R54" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V54" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="G55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="I55" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="K55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T55" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="H55" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S55" s="2"/>
-      <c r="T55" s="2" t="s">
+      <c r="U55" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U55" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="I56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="H56" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I56" s="2" t="s">
+      <c r="K56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T56" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="J56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="T56" s="2" t="s">
+      <c r="U56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V56" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="I57" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J57" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="H57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="K57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M57" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N57" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O57" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P57" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q57" s="2">
         <v>4.0</v>
       </c>
-      <c r="R57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S57" s="2"/>
-      <c r="T57" s="2" t="s">
+      <c r="R57" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V57" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V57" s="3"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="I58" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="H58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>35</v>
+      <c r="K58" s="2">
+        <v>5.0</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="M58" s="2">
+        <v>2.0</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="P58" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S58" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="T58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S58" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V58" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I59" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K59" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R59" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="K60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P60" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S60" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I62" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="K62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L62" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I63" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L63" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P63" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="R63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I67" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K67" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K68" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I69" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="K69" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L69" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M69" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N69" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O69" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R69" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S69" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T69" s="3"/>
+      <c r="U69" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="K71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N71" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T74" s="3"/>
+      <c r="U74" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I75" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="K75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M76" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R76" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T76" s="3"/>
+      <c r="U76" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
+      <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/NPS - matriz-tijuca.xlsx
+++ b/NPS - matriz-tijuca.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="507">
   <si>
     <t>userId</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Estamos interessados ​​em ouvir suas ideias! Por favor, compartilhe suas sugestões ou comentários</t>
   </si>
   <si>
-    <t>Tipo Respondente</t>
-  </si>
-  <si>
     <t>Perfil</t>
   </si>
   <si>
@@ -91,42 +88,214 @@
     <t>AÇÃO</t>
   </si>
   <si>
-    <t>Última atualização: 25/03/2026 18:30</t>
+    <t>Última atualização: 30/03/2026 14:47</t>
+  </si>
+  <si>
+    <t>Última atualização: 26/03/2026 14:30</t>
+  </si>
+  <si>
+    <t>67b49e6e5655554d6004a6ed</t>
+  </si>
+  <si>
+    <t>69b89948ff994cd629640f99</t>
+  </si>
+  <si>
+    <t>Queremos ouvir a sua opinião</t>
+  </si>
+  <si>
+    <t>matriz-tijuca</t>
+  </si>
+  <si>
+    <t>SOFIA GIL PAIM PEREIRA</t>
+  </si>
+  <si>
+    <t>sofiamt25164195@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>estudante</t>
+  </si>
+  <si>
+    <t>2026-03-30T15:04:41.768Z</t>
+  </si>
+  <si>
+    <t>10 - Extremamente provável</t>
+  </si>
+  <si>
+    <t>Colegio mt bom</t>
+  </si>
+  <si>
+    <t>6 - Muito Satisfeito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funcionarios bons,educadores bons diretoria maravilhosa </t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>679c1507e66a9c50eeecdb07</t>
+  </si>
+  <si>
+    <t>69b86abc21c08e4e2eff1f02</t>
+  </si>
+  <si>
+    <t>ALEXANDRE FERNANDES FEIJÓ</t>
+  </si>
+  <si>
+    <t>alexandre.f.feijo@gmail.com</t>
+  </si>
+  <si>
+    <t>responsavel</t>
+  </si>
+  <si>
+    <t>2026-03-30T15:02:41.603Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acredito ser uma escola normal, com a variante do app que facilita demais os comunicados </t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>699c6e7b264d0d99d573425a</t>
+  </si>
+  <si>
+    <t>LIDIANE SIQUEIRA SENA BENICÁ</t>
+  </si>
+  <si>
+    <t>dralidianesiqueirasena@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-28T18:31:33.904Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondendo a avaliação </t>
+  </si>
+  <si>
+    <t>67903682b3927051f589b1be</t>
+  </si>
+  <si>
+    <t>LUIZ FERNANDO ROQUE DE SOUZA</t>
+  </si>
+  <si>
+    <t>lfr.souza@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-28T11:36:05.955Z</t>
+  </si>
+  <si>
+    <t>0 - Nada provável</t>
+  </si>
+  <si>
+    <t>Tem que haver melhor interatividade com os pais!!!!!</t>
+  </si>
+  <si>
+    <t>1 - Muito Insatisfeito</t>
+  </si>
+  <si>
+    <t>O micro-ondas dever ser trocado, pois não esquenta as comidas quando necessário.</t>
+  </si>
+  <si>
+    <t>Detrator</t>
+  </si>
+  <si>
+    <t>698b92dfc88e1bbc7448d7d5</t>
+  </si>
+  <si>
+    <t>CAROLINA ANDREA SANTOS DA COSTA</t>
+  </si>
+  <si>
+    <t>carolindamas@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-26T15:35:48.333Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou gostando bastante do Colégio. Alguns pontos deixa a desejar, mas nada que mude a minha opinião. </t>
+  </si>
+  <si>
+    <t>Gosto do acolhimento da equipe e minhas filhas estão adorando. 
+Mas acredito que as regras devem valer para todos. Como regra, não pode usar casaco de time de futebol, ok? Recebi comunicado sobre a minha filha estar usando. A proibi. Porém vários outros estudantes continuam usando.</t>
+  </si>
+  <si>
+    <t>68783e6a23ec460ec65800ec</t>
+  </si>
+  <si>
+    <t>JORGE LUIZ FERREIRA NASCIMENTO</t>
+  </si>
+  <si>
+    <t>jorge.nascimento6@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-26T11:21:37.581Z</t>
+  </si>
+  <si>
+    <t>Percebo uma atenção especial dos professores com o meu filho e a cordialidade de todos os funcionários do colégio e a competência em resolver as solicitações em todas as vezes que preciso.</t>
+  </si>
+  <si>
+    <t>69a6fa607d0c0b0165848d55</t>
+  </si>
+  <si>
+    <t>FABIANA MOURÃO SILVA</t>
+  </si>
+  <si>
+    <t>fabianamouraos@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T22:45:02.264Z</t>
+  </si>
+  <si>
+    <t>Para vcs avaliarem nossa resposta.</t>
+  </si>
+  <si>
+    <t>Não tenho nada pra declarar no momento.</t>
+  </si>
+  <si>
+    <t>69449727c2b3b44d040b8abc</t>
+  </si>
+  <si>
+    <t>DENISE TORRES DE OLIVEIRA ROCHA</t>
+  </si>
+  <si>
+    <t>denisetor23@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T22:44:10.754Z</t>
+  </si>
+  <si>
+    <t>Pela receptividade, pelo conteúdo claro e objetivo, pelo meu filho estar gostando.</t>
+  </si>
+  <si>
+    <t>698bc812d7b0f7eb9bef4322</t>
+  </si>
+  <si>
+    <t>FERNANDA MELLO DA SILVA</t>
+  </si>
+  <si>
+    <t>fernandagabivini@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T21:39:42.697Z</t>
+  </si>
+  <si>
+    <t>Meu filho está muito mais estimulado!</t>
   </si>
   <si>
     <t>698bc812d7b0f7a720ef4319</t>
   </si>
   <si>
-    <t>69b86abc21c08e4e2eff1f02</t>
-  </si>
-  <si>
-    <t>Queremos ouvir a sua opinião</t>
-  </si>
-  <si>
-    <t>matriz-tijuca</t>
-  </si>
-  <si>
     <t>ISADORA TEIXEIRA COELHO16</t>
   </si>
   <si>
     <t>ruteleiateixeira@gmail.com</t>
   </si>
   <si>
-    <t>responsavel</t>
-  </si>
-  <si>
     <t>2026-03-25T21:02:22.713Z</t>
   </si>
   <si>
     <t>Acho que alguns profissionais deixam a desejar</t>
   </si>
   <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Neutro</t>
-  </si>
-  <si>
     <t>698bc812d7b0f7f91def433b</t>
   </si>
   <si>
@@ -139,43 +308,25 @@
     <t>2026-03-25T20:46:33.344Z</t>
   </si>
   <si>
-    <t>10 - Extremamente provável</t>
-  </si>
-  <si>
     <t>Tenho gostado muito das impressões desses primeiros meses. Observando e aguardando as próximas fases do ano, mas bastante feliz com a escolha.</t>
   </si>
   <si>
-    <t>6 - Muito Satisfeito</t>
-  </si>
-  <si>
     <t>As vezes me perco um pouco no layers. Fiz um pagamento da atividade extra JJ mas na verdade queria ter inscrito ele no teatro. Tentei mandar msg por lá no mesmo dia pedindo estorno, mas não sei pra onde foi. Perdi o prazo do teatro, mas aí foi minha falta de entendimento mesmo com a plataforma e fui ajudada pela secretaria... Enfim, ajustando os ponteiros mas creio que seja um sistema muito bom e estou curtindo tudo da escola! Inclusive e principalmente o incentivo aos alunos.</t>
   </si>
   <si>
-    <t>Promotor</t>
-  </si>
-  <si>
     <t>693221cc137069679a062cf5</t>
   </si>
   <si>
-    <t>69b89948ff994cd629640f99</t>
-  </si>
-  <si>
     <t>STELLA DA COSTA FERNANDES</t>
   </si>
   <si>
     <t>stellamt25183807@matrizeducacao.com.br</t>
   </si>
   <si>
-    <t>estudante</t>
-  </si>
-  <si>
     <t>2026-03-25T20:43:15.431Z</t>
   </si>
   <si>
     <t>Ótima experiência.</t>
-  </si>
-  <si>
-    <t>Aluno</t>
   </si>
   <si>
     <t>6960467df1a4c120b9b7696b</t>
@@ -325,7 +476,13 @@
 Caso não seja possível ampliar significativamente o tempo para todas as matérias, uma alternativa seria conceder um tempo adicional, pelo menos, para disciplinas que exigem maior desenvolvimento, como Matemática e Redação.</t>
   </si>
   <si>
-    <t>Detrator</t>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>Daniele Gomes</t>
+  </si>
+  <si>
+    <t>O Vincenzo está muito satisfeito, pois entendeu que, ao colocar a nota 5, seria uma boa avaliação.</t>
   </si>
   <si>
     <t>6984d0870d95f30333eba9a7</t>
@@ -344,6 +501,9 @@
   </si>
   <si>
     <t xml:space="preserve">Acho que deveria ter mais um tempo de avaliação de redação </t>
+  </si>
+  <si>
+    <t>Conversamos sobre o ocorrido do sumiço do material, inclusive enfatizei que estamos atuando com as famílias dos envolvidos.</t>
   </si>
   <si>
     <t>6941f3dfa0ddde04e45ad7b2</t>
@@ -1707,13 +1867,12 @@
     <col customWidth="1" min="18" max="18" width="69.38"/>
     <col customWidth="1" min="19" max="19" width="62.0"/>
     <col customWidth="1" min="20" max="20" width="395.75"/>
-    <col customWidth="1" min="21" max="21" width="14.25"/>
-    <col customWidth="1" min="22" max="22" width="7.75"/>
-    <col customWidth="1" min="23" max="23" width="12.75"/>
-    <col customWidth="1" min="24" max="24" width="24.13"/>
-    <col customWidth="1" min="25" max="25" width="16.38"/>
-    <col customWidth="1" min="26" max="26" width="5.25"/>
-    <col customWidth="1" min="27" max="27" width="28.63"/>
+    <col customWidth="1" min="21" max="21" width="7.75"/>
+    <col customWidth="1" min="22" max="22" width="12.75"/>
+    <col customWidth="1" min="23" max="23" width="24.13"/>
+    <col customWidth="1" min="24" max="24" width="16.38"/>
+    <col customWidth="1" min="25" max="25" width="5.25"/>
+    <col customWidth="1" min="26" max="27" width="28.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1824,46 +1983,46 @@
       <c r="H2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="2">
-        <v>7.0</v>
+      <c r="I2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T2" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="U2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V2" s="2"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
@@ -1872,10 +2031,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>29</v>
@@ -1884,59 +2043,55 @@
         <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>4.0</v>
       </c>
       <c r="M3" s="2">
         <v>5.0</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>44</v>
+      <c r="N3" s="2">
+        <v>5.0</v>
       </c>
       <c r="O3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V3" s="2"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
@@ -1945,10 +2100,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>29</v>
@@ -1963,51 +2118,49 @@
         <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="L4" s="2">
+        <v>3.0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4.0</v>
       </c>
       <c r="O4" s="2">
         <v>5.0</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>44</v>
+      <c r="P4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>5.0</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="S4" s="2">
+        <v>5.0</v>
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V4" s="2"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -2016,69 +2169,69 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K5" s="2">
+      <c r="M5" s="2">
         <v>4.0</v>
       </c>
-      <c r="L5" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="N5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O5" s="2">
         <v>4.0</v>
       </c>
-      <c r="O5" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>44</v>
+      <c r="P5" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="R5" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S5" s="2">
         <v>4.0</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T5" s="2"/>
+      <c r="T5" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="U5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="V5" s="2"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
@@ -2087,10 +2240,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>29</v>
@@ -2099,57 +2252,57 @@
         <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="2">
-        <v>5.0</v>
+        <v>66</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M6" s="2">
         <v>5.0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T6" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="U6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V6" s="2"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
@@ -2158,10 +2311,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>29</v>
@@ -2170,59 +2323,55 @@
         <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O7" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>70</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V7" s="2"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
@@ -2231,10 +2380,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -2243,28 +2392,28 @@
         <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>44</v>
+        <v>77</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>5.0</v>
       </c>
       <c r="M8" s="2">
         <v>5.0</v>
@@ -2272,28 +2421,28 @@
       <c r="N8" s="2">
         <v>5.0</v>
       </c>
-      <c r="O8" s="2">
-        <v>5.0</v>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>5.0</v>
       </c>
       <c r="R8" s="2">
         <v>5.0</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="2"/>
+      <c r="S8" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="U8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V8" s="2"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
@@ -2302,10 +2451,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -2314,57 +2463,55 @@
         <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V9" s="2"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
@@ -2373,10 +2520,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
@@ -2385,59 +2532,55 @@
         <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>44</v>
+        <v>88</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>4.0</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O10" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V10" s="2"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
@@ -2446,10 +2589,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
@@ -2458,57 +2601,55 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>92</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>44</v>
+        <v>93</v>
+      </c>
+      <c r="K11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O11" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5.0</v>
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V11" s="2"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
@@ -2517,10 +2658,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>29</v>
@@ -2529,57 +2670,57 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" s="2">
-        <v>5.0</v>
+        <v>98</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5.0</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P12" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T12" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="U12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V12" s="2"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
@@ -2588,10 +2729,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>29</v>
@@ -2600,59 +2741,55 @@
         <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="2">
-        <v>5.0</v>
+        <v>103</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M13" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="O13" s="2">
+        <v>5.0</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>102</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T13" s="2"/>
       <c r="U13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V13" s="2"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
@@ -2661,7 +2798,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -2673,59 +2810,55 @@
         <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I14" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K14" s="2">
         <v>4.0</v>
       </c>
       <c r="L14" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="N14" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O14" s="2">
+        <v>2.0</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="2">
+        <v>4.0</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>109</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T14" s="2"/>
       <c r="U14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V14" s="2"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
@@ -2757,48 +2890,44 @@
       <c r="H15" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="2">
-        <v>8.0</v>
+      <c r="I15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="K15" s="2">
-        <v>3.0</v>
+      <c r="K15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L15" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M15" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O15" s="2">
-        <v>4.0</v>
+        <v>37</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S15" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>115</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T15" s="2"/>
       <c r="U15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V15" s="2"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
@@ -2807,69 +2936,69 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T16" s="2"/>
       <c r="U16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V16" s="2"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
@@ -2881,7 +3010,7 @@
         <v>121</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2896,22 +3025,22 @@
         <v>123</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I17" s="2">
-        <v>7.0</v>
+      <c r="I17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K17" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L17" s="2">
-        <v>5.0</v>
+      <c r="K17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M17" s="2">
         <v>5.0</v>
@@ -2920,29 +3049,25 @@
         <v>5.0</v>
       </c>
       <c r="O17" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P17" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S17" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>126</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R17" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T17" s="2"/>
       <c r="U17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V17" s="2"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
@@ -2951,69 +3076,67 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V18" s="2"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
@@ -3022,69 +3145,69 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I19" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T19" s="2"/>
       <c r="U19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V19" s="2"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -3096,7 +3219,7 @@
         <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>29</v>
@@ -3111,51 +3234,49 @@
         <v>139</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>140</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="K20" s="2">
-        <v>5.0</v>
+      <c r="K20" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M20" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V20" s="2"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
@@ -3167,7 +3288,7 @@
         <v>142</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>29</v>
@@ -3182,53 +3303,49 @@
         <v>144</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>44</v>
+      <c r="K21" s="2">
+        <v>5.0</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="O21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T21" s="2"/>
       <c r="U21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V21" s="2"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
@@ -3237,7 +3354,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -3249,142 +3366,152 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I22" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M22" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T22" s="2" t="s">
+      <c r="U22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
+      <c r="W22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K23" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="W23" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I23" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
+      <c r="X23" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>29</v>
@@ -3393,57 +3520,57 @@
         <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I24" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K24" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="L24" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N24" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R24" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T24" s="2"/>
+        <v>4.0</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="U24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V24" s="2"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
@@ -3452,10 +3579,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>29</v>
@@ -3464,57 +3591,55 @@
         <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T25" s="2"/>
       <c r="U25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V25" s="2"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
@@ -3523,7 +3648,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>28</v>
@@ -3535,57 +3660,57 @@
         <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>42</v>
+        <v>177</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>44</v>
+        <v>178</v>
+      </c>
+      <c r="K26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T26" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="S26" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="U26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V26" s="2"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
@@ -3594,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>29</v>
@@ -3606,59 +3731,55 @@
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T27" s="2"/>
       <c r="U27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V27" s="2"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
@@ -3667,7 +3788,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>28</v>
@@ -3679,59 +3800,55 @@
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>42</v>
+        <v>188</v>
+      </c>
+      <c r="I28" s="2">
+        <v>9.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O28" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="L28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R28" s="2">
         <v>5.0</v>
       </c>
-      <c r="S28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="S28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T28" s="2"/>
       <c r="U28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V28" s="2"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
@@ -3740,10 +3857,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>29</v>
@@ -3752,57 +3869,55 @@
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>44</v>
+        <v>194</v>
+      </c>
+      <c r="K29" s="2">
+        <v>5.0</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="M29" s="2">
+        <v>5.0</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T29" s="2"/>
       <c r="U29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V29" s="2"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
@@ -3811,10 +3926,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -3823,57 +3938,57 @@
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>5.0</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T30" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="U30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V30" s="2"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
@@ -3882,10 +3997,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>29</v>
@@ -3894,57 +4009,57 @@
         <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I31" s="2">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N31" s="2">
-        <v>5.0</v>
+        <v>205</v>
+      </c>
+      <c r="K31" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P31" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R31" s="2">
         <v>5.0</v>
       </c>
       <c r="S31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T31" s="2"/>
+        <v>5.0</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="U31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V31" s="2"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
@@ -3953,7 +4068,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>28</v>
@@ -3965,40 +4080,40 @@
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I32" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K32" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L32" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M32" s="2">
-        <v>4.0</v>
+        <v>211</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N32" s="2">
         <v>5.0</v>
       </c>
-      <c r="O32" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P32" s="2">
-        <v>4.0</v>
+      <c r="O32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q32" s="2">
         <v>5.0</v>
@@ -4006,16 +4121,14 @@
       <c r="R32" s="2">
         <v>5.0</v>
       </c>
-      <c r="S32" s="2">
-        <v>5.0</v>
+      <c r="S32" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T32" s="2"/>
       <c r="U32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V32" s="2"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
@@ -4024,10 +4137,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>29</v>
@@ -4036,22 +4149,22 @@
         <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>42</v>
+        <v>215</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.0</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="K33" s="2">
         <v>5.0</v>
@@ -4065,8 +4178,8 @@
       <c r="N33" s="2">
         <v>5.0</v>
       </c>
-      <c r="O33" s="2" t="s">
-        <v>44</v>
+      <c r="O33" s="2">
+        <v>5.0</v>
       </c>
       <c r="P33" s="2">
         <v>5.0</v>
@@ -4082,11 +4195,9 @@
       </c>
       <c r="T33" s="2"/>
       <c r="U33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V33" s="2"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
@@ -4095,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>29</v>
@@ -4107,59 +4218,55 @@
         <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I34" s="2">
-        <v>8.0</v>
+        <v>220</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K34" s="2">
-        <v>5.0</v>
+        <v>221</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>216</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T34" s="2"/>
       <c r="U34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V34" s="2"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
@@ -4168,10 +4275,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>29</v>
@@ -4180,57 +4287,55 @@
         <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I35" s="2">
-        <v>8.0</v>
+        <v>225</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K35" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M35" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P35" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R35" s="2">
-        <v>4.0</v>
+        <v>226</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T35" s="2"/>
       <c r="U35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V35" s="2"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
@@ -4239,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>29</v>
@@ -4251,59 +4356,57 @@
         <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M36" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P36" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R36" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V36" s="2"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
@@ -4312,10 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -4324,59 +4427,57 @@
         <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="N37" s="2">
+        <v>5.0</v>
       </c>
       <c r="O37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>44</v>
+        <v>4.0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R37" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>5.0</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V37" s="2"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
@@ -4385,10 +4486,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>
@@ -4397,57 +4498,55 @@
         <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T38" s="2"/>
       <c r="U38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V38" s="2"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
@@ -4456,10 +4555,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
@@ -4468,59 +4567,55 @@
         <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N39" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>243</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T39" s="2"/>
       <c r="U39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V39" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V39" s="2"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
@@ -4529,10 +4624,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>29</v>
@@ -4541,57 +4636,55 @@
         <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I40" s="2">
         <v>9.0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>5.0</v>
+        <v>253</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N40" s="2">
         <v>5.0</v>
       </c>
-      <c r="O40" s="2">
-        <v>5.0</v>
+      <c r="O40" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P40" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q40" s="2">
-        <v>5.0</v>
+      <c r="Q40" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R40" s="2">
         <v>5.0</v>
       </c>
       <c r="S40" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V40" s="2"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
@@ -4600,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
@@ -4612,59 +4705,55 @@
         <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
+      </c>
+      <c r="I41" s="2">
+        <v>8.0</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>254</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="K41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P41" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T41" s="2"/>
       <c r="U41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V41" s="2"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
@@ -4673,10 +4762,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>29</v>
@@ -4685,25 +4774,25 @@
         <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>44</v>
+        <v>263</v>
+      </c>
+      <c r="K42" s="2">
+        <v>5.0</v>
       </c>
       <c r="L42" s="2">
         <v>5.0</v>
@@ -4711,31 +4800,29 @@
       <c r="M42" s="2">
         <v>5.0</v>
       </c>
-      <c r="N42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O42" s="2">
-        <v>4.0</v>
+      <c r="N42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P42" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>44</v>
+      <c r="Q42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>5.0</v>
       </c>
       <c r="T42" s="2"/>
       <c r="U42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V42" s="2"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
@@ -4744,10 +4831,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>29</v>
@@ -4756,59 +4843,57 @@
         <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>42</v>
+        <v>267</v>
+      </c>
+      <c r="I43" s="2">
+        <v>8.0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>44</v>
+        <v>268</v>
+      </c>
+      <c r="K43" s="2">
+        <v>5.0</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S43" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="S43" s="2">
+        <v>5.0</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V43" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V43" s="2"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
@@ -4817,10 +4902,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -4829,57 +4914,55 @@
         <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>42</v>
+        <v>273</v>
+      </c>
+      <c r="I44" s="2">
+        <v>8.0</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>44</v>
+        <v>274</v>
+      </c>
+      <c r="K44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L44" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N44" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P44" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q44" s="2">
         <v>5.0</v>
       </c>
-      <c r="R44" s="2" t="s">
-        <v>44</v>
+      <c r="R44" s="2">
+        <v>4.0</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T44" s="2"/>
       <c r="U44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V44" s="2"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
@@ -4888,10 +4971,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>29</v>
@@ -4900,57 +4983,57 @@
         <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K45" s="2">
-        <v>4.0</v>
+        <v>279</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N45" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P45" s="2">
         <v>5.0</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="2">
+        <v>5.0</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T45" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="U45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V45" s="2"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
@@ -4959,7 +5042,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>28</v>
@@ -4971,57 +5054,57 @@
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="O46" s="2">
+        <v>5.0</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T46" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="U46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V46" s="2"/>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
@@ -5030,10 +5113,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>29</v>
@@ -5042,57 +5125,55 @@
         <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T47" s="2"/>
       <c r="U47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V47" s="2"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
@@ -5101,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>29</v>
@@ -5113,59 +5194,57 @@
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K48" s="2">
-        <v>5.0</v>
+        <v>296</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="M48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N48" s="2">
+        <v>5.0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q48" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V48" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V48" s="2"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
@@ -5174,10 +5253,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>29</v>
@@ -5186,59 +5265,55 @@
         <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>42</v>
+        <v>300</v>
+      </c>
+      <c r="I49" s="2">
+        <v>9.0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>297</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="K49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T49" s="2"/>
       <c r="U49" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V49" s="2"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
@@ -5247,10 +5322,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>29</v>
@@ -5259,59 +5334,57 @@
         <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M50" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O50" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R50" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V50" s="2"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
@@ -5320,10 +5393,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -5332,57 +5405,55 @@
         <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="L51" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M51" s="2">
+        <v>5.0</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="O51" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P51" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T51" s="2"/>
       <c r="U51" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V51" s="2"/>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
@@ -5391,7 +5462,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>28</v>
@@ -5403,57 +5474,57 @@
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T52" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="U52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V52" s="2"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
@@ -5462,7 +5533,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>28</v>
@@ -5474,59 +5545,55 @@
         <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>5.0</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>319</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T53" s="2"/>
       <c r="U53" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V53" s="2"/>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
@@ -5535,7 +5602,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>28</v>
@@ -5547,57 +5614,55 @@
         <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="I54" s="2">
-        <v>9.0</v>
+        <v>327</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L54" s="2">
-        <v>5.0</v>
+        <v>328</v>
+      </c>
+      <c r="K54" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="N54" s="2">
+        <v>5.0</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="P54" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R54" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S54" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T54" s="2"/>
       <c r="U54" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V54" s="2"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
@@ -5606,10 +5671,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>29</v>
@@ -5618,59 +5683,55 @@
         <v>30</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I55" s="2">
-        <v>9.0</v>
+        <v>332</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="K55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M55" s="2">
-        <v>5.0</v>
+        <v>333</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>330</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T55" s="2"/>
       <c r="U55" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V55" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V55" s="2"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
@@ -5679,7 +5740,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>28</v>
@@ -5691,59 +5752,55 @@
         <v>30</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K56" s="2">
-        <v>5.0</v>
+        <v>338</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M56" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>336</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T56" s="2"/>
       <c r="U56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V56" s="2"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
@@ -5752,7 +5809,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>28</v>
@@ -5764,57 +5821,57 @@
         <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I57" s="2">
-        <v>8.0</v>
+        <v>342</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>44</v>
+        <v>343</v>
+      </c>
+      <c r="K57" s="2">
+        <v>5.0</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P57" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q57" s="2">
         <v>4.0</v>
       </c>
-      <c r="R57" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T57" s="2"/>
+      <c r="R57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>344</v>
+      </c>
       <c r="U57" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V57" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V57" s="2"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
@@ -5823,10 +5880,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -5835,57 +5892,57 @@
         <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="I58" s="2">
-        <v>9.0</v>
+        <v>348</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="K58" s="2">
-        <v>5.0</v>
+        <v>349</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M58" s="2">
-        <v>2.0</v>
+        <v>37</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P58" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S58" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="T58" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>350</v>
+      </c>
       <c r="U58" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V58" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V58" s="2"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
@@ -5894,10 +5951,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>29</v>
@@ -5906,59 +5963,57 @@
         <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="I59" s="2">
-        <v>8.0</v>
+        <v>354</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="K59" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L59" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N59" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P59" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>5.0</v>
+        <v>355</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R59" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S59" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V59" s="2"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
@@ -5967,10 +6022,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>29</v>
@@ -5979,59 +6034,55 @@
         <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="K60" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L60" s="2">
-        <v>5.0</v>
+        <v>361</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N60" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P60" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S60" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>358</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T60" s="2"/>
       <c r="U60" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V60" s="2"/>
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
@@ -6040,10 +6091,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>29</v>
@@ -6052,57 +6103,55 @@
         <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T61" s="2"/>
       <c r="U61" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V61" s="2"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
@@ -6111,10 +6160,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>29</v>
@@ -6123,57 +6172,57 @@
         <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="I62" s="2">
-        <v>7.0</v>
+        <v>370</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="K62" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L62" s="2">
-        <v>4.0</v>
+        <v>371</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P62" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q62" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R62" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S62" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T62" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>372</v>
+      </c>
       <c r="U62" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V62" s="2"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
@@ -6182,10 +6231,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>29</v>
@@ -6194,57 +6243,55 @@
         <v>30</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="I63" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L63" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M63" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N63" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O63" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P63" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="Q63" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R63" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S63" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T63" s="2"/>
       <c r="U63" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V63" s="2"/>
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
@@ -6253,10 +6300,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>29</v>
@@ -6265,59 +6312,57 @@
         <v>30</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>42</v>
+        <v>381</v>
+      </c>
+      <c r="I64" s="2">
+        <v>9.0</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>44</v>
+        <v>382</v>
+      </c>
+      <c r="K64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M64" s="2">
+        <v>5.0</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>4.0</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V64" s="2"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
@@ -6326,10 +6371,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -6338,57 +6383,57 @@
         <v>30</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K65" s="2">
         <v>5.0</v>
       </c>
-      <c r="L65" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>44</v>
+      <c r="L65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M65" s="2">
+        <v>5.0</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T65" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="R65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>389</v>
+      </c>
       <c r="U65" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V65" s="2"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
@@ -6397,10 +6442,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>29</v>
@@ -6409,28 +6454,28 @@
         <v>30</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>42</v>
+        <v>393</v>
+      </c>
+      <c r="I66" s="2">
+        <v>8.0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="K66" s="2">
-        <v>5.0</v>
+        <v>394</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M66" s="2">
         <v>5.0</v>
@@ -6441,27 +6486,23 @@
       <c r="O66" s="2">
         <v>5.0</v>
       </c>
-      <c r="P66" s="2" t="s">
-        <v>44</v>
+      <c r="P66" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q66" s="2">
         <v>4.0</v>
       </c>
       <c r="R66" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S66" s="2">
         <v>5.0</v>
       </c>
-      <c r="T66" s="2" t="s">
-        <v>390</v>
-      </c>
+      <c r="T66" s="2"/>
       <c r="U66" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V66" s="2"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
@@ -6470,7 +6511,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>28</v>
@@ -6482,59 +6523,55 @@
         <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I67" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="K67" s="2">
         <v>5.0</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="M67" s="2">
+        <v>2.0</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="P67" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S67" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>396</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S67" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T67" s="2"/>
       <c r="U67" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V67" s="2"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
@@ -6543,10 +6580,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>29</v>
@@ -6555,59 +6592,57 @@
         <v>30</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>42</v>
+        <v>403</v>
+      </c>
+      <c r="I68" s="2">
+        <v>8.0</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K68" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R68" s="2">
         <v>4.0</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P68" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>44</v>
+      <c r="S68" s="2">
+        <v>4.0</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V68" s="2"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
@@ -6616,7 +6651,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>28</v>
@@ -6628,57 +6663,57 @@
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="I69" s="2">
-        <v>6.0</v>
+        <v>409</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K69" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="L69" s="2">
         <v>5.0</v>
       </c>
-      <c r="M69" s="2">
-        <v>3.0</v>
+      <c r="M69" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N69" s="2">
         <v>5.0</v>
       </c>
-      <c r="O69" s="2">
-        <v>5.0</v>
+      <c r="O69" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P69" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q69" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R69" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S69" s="2">
         <v>4.0</v>
       </c>
-      <c r="T69" s="3"/>
+      <c r="T69" s="2" t="s">
+        <v>411</v>
+      </c>
       <c r="U69" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V69" s="2"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
@@ -6687,10 +6722,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>29</v>
@@ -6699,59 +6734,55 @@
         <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M70" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T70" s="2" t="s">
-        <v>413</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T70" s="2"/>
       <c r="U70" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V70" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V70" s="2"/>
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
@@ -6760,7 +6791,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>28</v>
@@ -6772,59 +6803,55 @@
         <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>42</v>
+        <v>420</v>
+      </c>
+      <c r="I71" s="2">
+        <v>7.0</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K71" s="2">
         <v>5.0</v>
       </c>
       <c r="L71" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M71" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N71" s="2">
         <v>4.0</v>
       </c>
+      <c r="M71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="O71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>419</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="P71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T71" s="2"/>
       <c r="U71" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V71" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V71" s="2"/>
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
@@ -6833,7 +6860,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>28</v>
@@ -6845,59 +6872,55 @@
         <v>30</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>42</v>
+        <v>425</v>
+      </c>
+      <c r="I72" s="2">
+        <v>7.0</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>425</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L72" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M72" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N72" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O72" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P72" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="R72" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T72" s="2"/>
       <c r="U72" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V72" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V72" s="2"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
@@ -6906,10 +6929,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>29</v>
@@ -6918,59 +6941,57 @@
         <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V73" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V73" s="2"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
@@ -6979,7 +7000,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>28</v>
@@ -6991,57 +7012,55 @@
         <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M74" s="2">
-        <v>5.0</v>
+        <v>437</v>
+      </c>
+      <c r="K74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R74" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T74" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="T74" s="2"/>
       <c r="U74" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V74" s="2"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
@@ -7050,10 +7069,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>29</v>
@@ -7062,59 +7081,57 @@
         <v>30</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="I75" s="2">
-        <v>9.0</v>
+        <v>441</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K75" s="2">
         <v>5.0</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="M75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>5.0</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S75" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S75" s="2">
+        <v>5.0</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V75" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V75" s="2"/>
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
@@ -7123,10 +7140,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>29</v>
@@ -7135,57 +7152,57 @@
         <v>30</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>42</v>
+        <v>447</v>
+      </c>
+      <c r="I76" s="2">
+        <v>7.0</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>44</v>
+        <v>448</v>
+      </c>
+      <c r="K76" s="2">
+        <v>5.0</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M76" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R76" s="2">
-        <v>4.0</v>
+        <v>37</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T76" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="U76" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V76" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V76" s="2"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
@@ -7194,10 +7211,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>29</v>
@@ -7206,65 +7223,692 @@
         <v>30</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>44</v>
+        <v>454</v>
+      </c>
+      <c r="K77" s="2">
+        <v>4.0</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="P77" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="U77" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="V77" s="2"/>
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="I78" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="K78" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L78" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M78" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N78" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O78" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P78" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R78" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S78" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T78" s="2"/>
+      <c r="U78" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V78" s="2"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="3"/>
+      <c r="AA78" s="3"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M79" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V79" s="2"/>
+      <c r="W79" s="3"/>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
+      <c r="Z79" s="3"/>
+      <c r="AA79" s="3"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="K80" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L80" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M80" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N80" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V80" s="2"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="3"/>
+      <c r="AA80" s="3"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T81" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="U81" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V81" s="2"/>
+      <c r="W81" s="3"/>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
+      <c r="Z81" s="3"/>
+      <c r="AA81" s="3"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T82" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V82" s="2"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T83" s="2"/>
+      <c r="U83" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+      <c r="Z83" s="3"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I84" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="K84" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T84" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="3"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M85" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R85" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T85" s="3"/>
+      <c r="U85" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
+      <c r="Z85" s="3"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
